--- a/Backoffice/plugins/upr/static/templates/unified_country_plan.xlsx
+++ b/Backoffice/plugins/upr/static/templates/unified_country_plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifrcorg.sharepoint.com/sites/THEFDRSTEAM/Shared Documents/Unified Planning and Reporting/2027 Planning/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humanitarian Databank\Backoffice\plugins\upr\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{104EA9F8-BE25-42B4-889F-BD144B2E32A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D71F05C5-509A-4802-885D-CD4921385F99}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D6C1B8-777F-4625-8DE3-B4DB342B5356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12945" yWindow="-21720" windowWidth="51840" windowHeight="21120" tabRatio="717" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="717" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TemplateData" sheetId="1" state="hidden" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -6595,30 +6595,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6631,45 +6615,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -6694,6 +6644,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
       <protection hidden="1"/>
@@ -6709,6 +6663,52 @@
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -6735,28 +6735,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -6772,9 +6750,31 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6823,10 +6823,11 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -39804,13 +39805,13 @@
     <row r="6" spans="2:16" ht="19.2" customHeight="1">
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="162" t="str" cm="1">
+      <c r="D6" s="149" t="str" cm="1">
         <f t="array" ref="D6">TR("T04")</f>
         <v>Cell open for input</v>
       </c>
       <c r="E6" s="139"/>
       <c r="F6" s="24"/>
-      <c r="G6" s="159" t="str" cm="1">
+      <c r="G6" s="145" t="str" cm="1">
         <f t="array" ref="G6">TR("T05")</f>
         <v>Cell Locked (or Automatically prefilled)</v>
       </c>
@@ -39819,7 +39820,7 @@
       <c r="J6" s="139"/>
       <c r="K6" s="139"/>
       <c r="L6" s="139"/>
-      <c r="N6" s="155" t="str" cm="1">
+      <c r="N6" s="141" t="str" cm="1">
         <f t="array" ref="N6">TR("T06")</f>
         <v>Guidance</v>
       </c>
@@ -39845,24 +39846,24 @@
     </row>
     <row r="8" spans="2:16" ht="27.6" customHeight="1">
       <c r="B8" s="24"/>
-      <c r="C8" s="161" t="str" cm="1">
+      <c r="C8" s="148" t="str" cm="1">
         <f t="array" ref="C8">TR("T55")</f>
         <v xml:space="preserve">USE THIS TEMPLATE ONLY IF YOU HAVE CONNECTIVITY ISSUES AND CAN'T ACCESS THE </v>
       </c>
-      <c r="D8" s="161"/>
-      <c r="E8" s="161"/>
-      <c r="F8" s="161"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
-      <c r="I8" s="161"/>
-      <c r="J8" s="161"/>
-      <c r="K8" s="161"/>
-      <c r="L8" s="161"/>
-      <c r="M8" s="163" t="s">
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="150" t="s">
         <v>1704</v>
       </c>
-      <c r="N8" s="163"/>
-      <c r="O8" s="163"/>
+      <c r="N8" s="150"/>
+      <c r="O8" s="150"/>
       <c r="P8" s="24"/>
     </row>
     <row r="9" spans="2:16" ht="14.55" customHeight="1">
@@ -39923,43 +39924,43 @@
       <c r="P11" s="28"/>
     </row>
     <row r="12" spans="2:16" ht="14.55" customHeight="1">
-      <c r="B12" s="160" t="str">
+      <c r="B12" s="147" t="str">
         <f>TR("T08")</f>
         <v>Region</v>
       </c>
-      <c r="C12" s="132"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="156" t="str">
+      <c r="C12" s="155"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="142" t="str">
         <f>TR("T09")</f>
         <v>Country</v>
       </c>
       <c r="H12" s="139"/>
       <c r="I12" s="139"/>
-      <c r="J12" s="157"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="133"/>
-      <c r="M12" s="133"/>
-      <c r="N12" s="133"/>
-      <c r="O12" s="134"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="163"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="156"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="157"/>
       <c r="P12" s="30"/>
     </row>
     <row r="13" spans="2:16" ht="12.6" customHeight="1">
       <c r="B13" s="139"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="158"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="144"/>
       <c r="H13" s="139"/>
       <c r="I13" s="139"/>
-      <c r="J13" s="157"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="136"/>
-      <c r="M13" s="136"/>
-      <c r="N13" s="136"/>
-      <c r="O13" s="137"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="158"/>
+      <c r="L13" s="159"/>
+      <c r="M13" s="159"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="160"/>
       <c r="P13" s="30"/>
     </row>
     <row r="14" spans="2:16" ht="9.6" customHeight="1">
@@ -39981,25 +39982,25 @@
     </row>
     <row r="15" spans="2:16" ht="24.6" customHeight="1">
       <c r="B15" s="30"/>
-      <c r="C15" s="144" t="str" cm="1">
+      <c r="C15" s="132" t="str" cm="1">
         <f t="array" ref="C15">TR("T10")</f>
         <v>Emergency Appeal 1</v>
       </c>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="145"/>
-      <c r="G15" s="145"/>
-      <c r="H15" s="146"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="134"/>
       <c r="I15" s="31"/>
-      <c r="J15" s="144" t="str" cm="1">
+      <c r="J15" s="132" t="str" cm="1">
         <f t="array" ref="J15">TR("T11")</f>
         <v>Emergency Appeal 2</v>
       </c>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="145"/>
-      <c r="N15" s="145"/>
-      <c r="O15" s="146"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="134"/>
       <c r="P15" s="30"/>
     </row>
     <row r="16" spans="2:16" ht="21" customHeight="1">
@@ -40009,9 +40010,9 @@
         <f>TR("T12")</f>
         <v>MDR code</v>
       </c>
-      <c r="E16" s="140"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="142"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="137"/>
       <c r="H16" s="33"/>
       <c r="I16" s="31"/>
       <c r="J16" s="34"/>
@@ -40019,9 +40020,9 @@
         <f>TR("T12")</f>
         <v>MDR code</v>
       </c>
-      <c r="L16" s="140"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="142"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="137"/>
       <c r="O16" s="33"/>
       <c r="P16" s="35"/>
     </row>
@@ -40049,9 +40050,9 @@
         <f>TR("T13")</f>
         <v>Name</v>
       </c>
-      <c r="E18" s="140"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="142"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="137"/>
       <c r="H18" s="33"/>
       <c r="I18" s="31"/>
       <c r="J18" s="32"/>
@@ -40059,9 +40060,9 @@
         <f>TR("T13")</f>
         <v>Name</v>
       </c>
-      <c r="L18" s="140"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="142"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="137"/>
       <c r="O18" s="36"/>
       <c r="P18" s="30"/>
     </row>
@@ -40101,15 +40102,15 @@
     </row>
     <row r="21" spans="2:16" ht="23.4" customHeight="1">
       <c r="B21" s="30"/>
-      <c r="C21" s="144" t="str" cm="1">
+      <c r="C21" s="132" t="str" cm="1">
         <f t="array" ref="C21">TR("T14")</f>
         <v>Emergency Appeal 3</v>
       </c>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="145"/>
-      <c r="H21" s="146"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="134"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
@@ -40126,9 +40127,9 @@
         <f>TR("T12")</f>
         <v>MDR code</v>
       </c>
-      <c r="E22" s="140"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="142"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="137"/>
       <c r="H22" s="33"/>
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
@@ -40163,9 +40164,9 @@
         <f>TR("T13")</f>
         <v>Name</v>
       </c>
-      <c r="E24" s="140"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="142"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="137"/>
       <c r="H24" s="33"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
@@ -40252,20 +40253,20 @@
         <f t="array" ref="B29">TR("T16")</f>
         <v>Volunteers</v>
       </c>
-      <c r="C29" s="152" t="str">
+      <c r="C29" s="146" t="str">
         <f t="array" ref="C29">IFERROR(_xlfn._xlws.FILTER(UPR[ValueNum],(UPR[Country]=Data_Country)*(UPR[Indicator]="Number of people volunteering")),"")</f>
         <v/>
       </c>
-      <c r="D29" s="142"/>
+      <c r="D29" s="137"/>
       <c r="E29" s="29" t="str" cm="1">
         <f t="array" ref="E29">TR("T17")</f>
         <v>Staff</v>
       </c>
-      <c r="F29" s="152" t="str">
+      <c r="F29" s="146" t="str">
         <f t="array" ref="F29">IFERROR(_xlfn._xlws.FILTER(UPR[ValueNum],(UPR[Country]=Data_Country)*(UPR[Indicator]="Number of paid staff")),"")</f>
         <v/>
       </c>
-      <c r="G29" s="142"/>
+      <c r="G29" s="137"/>
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
       <c r="K29" s="106" t="str" cm="1">
@@ -40307,13 +40308,13 @@
         <f>IF(COUNTIFS(FDRS[Country],Data_Country,FDRS[Year],2024)=0,"","FDRS 2024 -&gt;")</f>
         <v/>
       </c>
-      <c r="C31" s="138" t="str">
+      <c r="C31" s="161" t="str">
         <f t="array" ref="C31">IFERROR(_xlfn._xlws.FILTER(FDRS[Value],(FDRS[Country]=Data_Country)*(FDRS[Attribute]="Volunteers"))&amp;"","")</f>
         <v/>
       </c>
       <c r="D31" s="139"/>
       <c r="E31" s="41"/>
-      <c r="F31" s="143" t="str">
+      <c r="F31" s="162" t="str">
         <f t="array" ref="F31">IFERROR(_xlfn._xlws.FILTER(FDRS[Value],(FDRS[Country]=Data_Country)*(FDRS[Attribute]="Staff"))&amp;" ","")</f>
         <v/>
       </c>
@@ -40336,7 +40337,7 @@
     </row>
     <row r="32" spans="2:16" ht="18.600000000000001" customHeight="1">
       <c r="B32" s="101"/>
-      <c r="C32" s="154"/>
+      <c r="C32" s="140"/>
       <c r="D32" s="139"/>
       <c r="E32" s="24"/>
       <c r="F32" s="102"/>
@@ -40353,7 +40354,7 @@
     </row>
     <row r="33" spans="2:16" ht="43.2" customHeight="1">
       <c r="B33" s="24"/>
-      <c r="C33" s="151" t="str" cm="1">
+      <c r="C33" s="154" t="str" cm="1">
         <f t="array" ref="C33">TR("T39")</f>
         <v>Figures for volunteers, staff, local units, and branches have been prefilled if the National Society has provided its data for 2025 unified annual reporting.
 Please review and update these numbers if needed. FDRS 2024 figures have been listed only for reference.</v>
@@ -40391,7 +40392,7 @@
     </row>
     <row r="35" spans="2:16" ht="17.399999999999999" customHeight="1">
       <c r="B35" s="24"/>
-      <c r="C35" s="150" t="str" cm="1">
+      <c r="C35" s="153" t="str" cm="1">
         <f t="array" ref="C35">TR("T18")</f>
         <v>Local Units</v>
       </c>
@@ -40400,7 +40401,7 @@
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
-      <c r="I35" s="153" t="str" cm="1">
+      <c r="I35" s="138" t="str" cm="1">
         <f t="array" ref="I35">TR("T19")</f>
         <v>Branches</v>
       </c>
@@ -40414,7 +40415,7 @@
     </row>
     <row r="36" spans="2:16" ht="48" customHeight="1">
       <c r="B36" s="24"/>
-      <c r="C36" s="148" t="str" cm="1">
+      <c r="C36" s="151" t="str" cm="1">
         <f t="array" ref="C36">TR("T40")</f>
         <v>ALL subdivisions of a National Society that coordinate and deliver services to people.
 These include ALL levels (provincial, state, city, district branches, sections or chapters,
@@ -40425,7 +40426,7 @@
       <c r="F36" s="139"/>
       <c r="G36" s="139"/>
       <c r="H36" s="103"/>
-      <c r="I36" s="148" t="str" cm="1">
+      <c r="I36" s="151" t="str" cm="1">
         <f t="array" ref="I36">TR("T41")</f>
         <v>A Branch has its roles and responsibilities and relationship with the National Headquarters defined through National Societies’ Statutes,
 including the level of autonomy given, especially in its legal status, mobilizing local resources,
@@ -40442,13 +40443,13 @@
     </row>
     <row r="37" spans="2:16" ht="71.400000000000006" customHeight="1">
       <c r="B37" s="24"/>
-      <c r="C37" s="149"/>
+      <c r="C37" s="152"/>
       <c r="D37" s="139"/>
       <c r="E37" s="139"/>
       <c r="F37" s="139"/>
       <c r="G37" s="139"/>
       <c r="H37" s="103"/>
-      <c r="I37" s="149"/>
+      <c r="I37" s="152"/>
       <c r="J37" s="139"/>
       <c r="K37" s="139"/>
       <c r="L37" s="139"/>
@@ -40495,6 +40496,21 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="MYnWBUuXuFRj8S/col0Z2iS1mHB9AQ29NgDyazkd5wJU3rdfURcu9xIkZibNC4zQPLkuRpNO/Y6FfJ2YNnHWiw==" saltValue="yk1jF30Ss8tKmO5ycvQ34A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="31">
+    <mergeCell ref="B10:P10"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="J15:O15"/>
+    <mergeCell ref="K12:O13"/>
+    <mergeCell ref="C36:G37"/>
+    <mergeCell ref="I36:O37"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C33:O33"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="E24:G24"/>
@@ -40511,21 +40527,6 @@
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="C36:G37"/>
-    <mergeCell ref="I36:O37"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C33:O33"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B10:P10"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="J15:O15"/>
-    <mergeCell ref="K12:O13"/>
   </mergeCells>
   <conditionalFormatting sqref="K12">
     <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
@@ -40998,7 +40999,7 @@
     </row>
     <row r="2" spans="1:11" ht="33.6" customHeight="1">
       <c r="A2" s="92"/>
-      <c r="B2" s="178" t="str">
+      <c r="B2" s="172" t="str">
         <f>TR("T25")</f>
         <v>Planned Bilateral Support</v>
       </c>
@@ -41009,7 +41010,7 @@
       <c r="G2" s="170"/>
       <c r="H2" s="170"/>
       <c r="I2" s="170"/>
-      <c r="J2" s="179"/>
+      <c r="J2" s="173"/>
       <c r="K2" s="65"/>
     </row>
     <row r="3" spans="1:11" ht="43.2" customHeight="1">
@@ -41018,7 +41019,7 @@
         <f>TR("T08")</f>
         <v>Region</v>
       </c>
-      <c r="C3" s="177" t="str">
+      <c r="C3" s="171" t="str">
         <f>TR("T26")</f>
         <v>Participating National Society name</v>
       </c>
@@ -41054,7 +41055,7 @@
       <c r="B4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="177" t="s">
         <v>1481</v>
       </c>
       <c r="D4" s="170"/>
@@ -41083,8 +41084,8 @@
     <row r="5" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A5" s="92"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="175"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -41099,8 +41100,8 @@
     <row r="6" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A6" s="92"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="174"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="175"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -41115,8 +41116,8 @@
     <row r="7" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A7" s="92"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="174"/>
+      <c r="C7" s="178"/>
+      <c r="D7" s="175"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -41131,8 +41132,8 @@
     <row r="8" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A8" s="92"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="174"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="175"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -41147,8 +41148,8 @@
     <row r="9" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A9" s="92"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="174"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="175"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -41163,8 +41164,8 @@
     <row r="10" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A10" s="92"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="175"/>
-      <c r="D10" s="174"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="175"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
@@ -41179,8 +41180,8 @@
     <row r="11" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A11" s="92"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="174"/>
+      <c r="C11" s="178"/>
+      <c r="D11" s="175"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -41195,8 +41196,8 @@
     <row r="12" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A12" s="92"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="175"/>
-      <c r="D12" s="174"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="175"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -41211,8 +41212,8 @@
     <row r="13" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A13" s="92"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="174"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="175"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
@@ -41227,8 +41228,8 @@
     <row r="14" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A14" s="92"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="175"/>
-      <c r="D14" s="174"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="175"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -41243,8 +41244,8 @@
     <row r="15" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A15" s="92"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="174"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="175"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -41259,8 +41260,8 @@
     <row r="16" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A16" s="92"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="175"/>
-      <c r="D16" s="174"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="175"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
@@ -41275,8 +41276,8 @@
     <row r="17" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A17" s="92"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="174"/>
+      <c r="C17" s="178"/>
+      <c r="D17" s="175"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
@@ -41291,8 +41292,8 @@
     <row r="18" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A18" s="92"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="174"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="175"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -41307,8 +41308,8 @@
     <row r="19" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A19" s="92"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="174"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="175"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
@@ -41323,8 +41324,8 @@
     <row r="20" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A20" s="92"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="174"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="175"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
@@ -41339,8 +41340,8 @@
     <row r="21" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A21" s="92"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="174"/>
+      <c r="C21" s="178"/>
+      <c r="D21" s="175"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
@@ -41355,8 +41356,8 @@
     <row r="22" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A22" s="92"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="174"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="175"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
@@ -41371,8 +41372,8 @@
     <row r="23" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A23" s="92"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="174"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="175"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
@@ -41387,8 +41388,8 @@
     <row r="24" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A24" s="92"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="174"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="175"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -41403,8 +41404,8 @@
     <row r="25" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A25" s="92"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="174"/>
+      <c r="C25" s="178"/>
+      <c r="D25" s="175"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
@@ -41419,8 +41420,8 @@
     <row r="26" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A26" s="92"/>
       <c r="B26" s="11"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="174"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="175"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -41435,8 +41436,8 @@
     <row r="27" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A27" s="92"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="174"/>
+      <c r="C27" s="178"/>
+      <c r="D27" s="175"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
@@ -41451,8 +41452,8 @@
     <row r="28" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A28" s="92"/>
       <c r="B28" s="11"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="174"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="175"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -41467,8 +41468,8 @@
     <row r="29" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A29" s="92"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="174"/>
+      <c r="C29" s="178"/>
+      <c r="D29" s="175"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -41483,8 +41484,8 @@
     <row r="30" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A30" s="92"/>
       <c r="B30" s="11"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="174"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="175"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -41499,8 +41500,8 @@
     <row r="31" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A31" s="92"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="174"/>
+      <c r="C31" s="178"/>
+      <c r="D31" s="175"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
@@ -41515,8 +41516,8 @@
     <row r="32" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A32" s="92"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="175"/>
-      <c r="D32" s="174"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="175"/>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -41531,8 +41532,8 @@
     <row r="33" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A33" s="92"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="174"/>
+      <c r="C33" s="178"/>
+      <c r="D33" s="175"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
@@ -41547,8 +41548,8 @@
     <row r="34" spans="1:11" ht="20.399999999999999" customHeight="1">
       <c r="A34" s="92"/>
       <c r="B34" s="22"/>
-      <c r="C34" s="171"/>
-      <c r="D34" s="172"/>
+      <c r="C34" s="179"/>
+      <c r="D34" s="180"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -41576,24 +41577,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="49XiNOYKy5tipRC1XvN/CtRq4GaDLZO+OwAhNJU9S9YsyyLtYca3l8+T9OwuQ/KCjwKQDmkNPHAuhqjXvE+QLA==" saltValue="L96SNDdMC/MMsiBk0GrUhA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="34">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C30:D30"/>
@@ -41610,6 +41593,24 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
     <cfRule type="expression" dxfId="12" priority="1">
@@ -41821,7 +41822,7 @@
       <c r="T4" s="170"/>
       <c r="U4" s="170"/>
       <c r="V4" s="170"/>
-      <c r="W4" s="179"/>
+      <c r="W4" s="173"/>
       <c r="X4" s="86"/>
       <c r="Y4" s="122"/>
     </row>
@@ -44062,7 +44063,7 @@
       <c r="N12" s="77"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0jp2yZlub+66m4CvmuRBd3A8WJ6udwV1AYhDlBQWbhOTvKQ3gfLAIgwKwp9J3csFwsH3ueiZiNRgt7xDCiVn4Q==" saltValue="LjU2mVmMPScX5HuMkwCUAg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XAjLx/H/V6e63hwC5BdtigSvDMgudePJZ6A1fNp5psXoaomGAZbFETeIe1oAP/NoypstBKW/ySrQRP3ckVn+Wg==" saltValue="CqVxI7h3kU5lJp4HQYHJCA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B4:M11"/>
   </mergeCells>
@@ -44071,15 +44072,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Summary xmlns="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffb314bc-7b2d-45ce-a517-7d370eafd82d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44346,21 +44344,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Summary xmlns="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffb314bc-7b2d-45ce-a517-7d370eafd82d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E974020-0709-451F-86D8-75178B10225A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE46BC1E-73EA-4AAC-A11E-6C08D8813737}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad"/>
-    <ds:schemaRef ds:uri="ffb314bc-7b2d-45ce-a517-7d370eafd82d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -44385,9 +44383,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE46BC1E-73EA-4AAC-A11E-6C08D8813737}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E974020-0709-451F-86D8-75178B10225A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="67bd97f6-f5f5-4f29-8f0d-e757ed3ec3ad"/>
+    <ds:schemaRef ds:uri="ffb314bc-7b2d-45ce-a517-7d370eafd82d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>